--- a/ig/DM-DECEMBRE-2024/ValueSet-JDV-J14-QualiteRepresentantLegal-CISIS.xlsx
+++ b/ig/DM-DECEMBRE-2024/ValueSet-JDV-J14-QualiteRepresentantLegal-CISIS.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="119">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20240126120000</t>
+    <t>20241121120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-26T12:00:00+01:00</t>
+    <t>2024-11-21T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -639,7 +639,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B47"/>
+  <dimension ref="A1:B46"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -904,121 +904,113 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>41</v>
+        <v>93</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="B47" t="s" s="2">
         <v>118</v>
       </c>
     </row>
